--- a/tests/testthat/test_xlsx_files/data_to_worksheet.xlsx
+++ b/tests/testthat/test_xlsx_files/data_to_worksheet.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CLD16492\Documents\Projects\BETAexcel\tests\testthat\test_xlsx_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\code\xlr\tests\testthat\test_xlsx_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C4C65E-02CB-4F35-89E9-9F9B96B2CBDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13130" windowHeight="6110"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test 1" sheetId="5" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="13">
   <si>
     <t>mpg</t>
   </si>
@@ -56,11 +57,14 @@
   <si>
     <t>test</t>
   </si>
+  <si>
+    <t>scientific</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
@@ -108,7 +112,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -134,12 +138,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -162,7 +186,7 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -172,6 +196,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -470,11 +503,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L36"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -487,7 +520,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -521,8 +554,11 @@
       <c r="K2" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L2" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>21</v>
       </c>
@@ -556,8 +592,11 @@
       <c r="K3" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L3" s="13">
+        <v>16.46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>21</v>
       </c>
@@ -591,8 +630,11 @@
       <c r="K4" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L4" s="13">
+        <v>17.02</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>22.8</v>
       </c>
@@ -626,8 +668,11 @@
       <c r="K5" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L5" s="13">
+        <v>18.61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>21.4</v>
       </c>
@@ -661,8 +706,11 @@
       <c r="K6" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L6" s="13">
+        <v>19.440000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>18.7</v>
       </c>
@@ -696,8 +744,11 @@
       <c r="K7" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L7" s="13">
+        <v>17.02</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>18.100000000000001</v>
       </c>
@@ -731,8 +782,11 @@
       <c r="K8" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L8" s="13">
+        <v>20.22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>14.3</v>
       </c>
@@ -766,8 +820,11 @@
       <c r="K9" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L9" s="13">
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>24.4</v>
       </c>
@@ -801,8 +858,11 @@
       <c r="K10" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L10" s="13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>22.8</v>
       </c>
@@ -836,8 +896,11 @@
       <c r="K11" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L11" s="13">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>19.2</v>
       </c>
@@ -871,8 +934,11 @@
       <c r="K12" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L12" s="13">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>17.8</v>
       </c>
@@ -906,8 +972,11 @@
       <c r="K13" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L13" s="13">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>16.399999999999999</v>
       </c>
@@ -941,8 +1010,11 @@
       <c r="K14" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L14" s="13">
+        <v>17.399999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>17.3</v>
       </c>
@@ -976,8 +1048,11 @@
       <c r="K15" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L15" s="13">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15.2</v>
       </c>
@@ -1011,8 +1086,11 @@
       <c r="K16" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L16" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>10.4</v>
       </c>
@@ -1046,8 +1124,11 @@
       <c r="K17" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L17" s="13">
+        <v>17.98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>10.4</v>
       </c>
@@ -1081,8 +1162,11 @@
       <c r="K18" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L18" s="13">
+        <v>17.82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>14.7</v>
       </c>
@@ -1116,8 +1200,11 @@
       <c r="K19" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L19" s="13">
+        <v>17.420000000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>32.4</v>
       </c>
@@ -1151,8 +1238,11 @@
       <c r="K20" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L20" s="13">
+        <v>19.47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>30.4</v>
       </c>
@@ -1186,8 +1276,11 @@
       <c r="K21" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L21" s="13">
+        <v>18.52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>33.9</v>
       </c>
@@ -1221,8 +1314,11 @@
       <c r="K22" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L22" s="13">
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21.5</v>
       </c>
@@ -1256,8 +1352,11 @@
       <c r="K23" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L23" s="13">
+        <v>20.010000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>15.5</v>
       </c>
@@ -1291,8 +1390,11 @@
       <c r="K24" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L24" s="13">
+        <v>16.87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>15.2</v>
       </c>
@@ -1326,8 +1428,11 @@
       <c r="K25" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L25" s="13">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>13.3</v>
       </c>
@@ -1361,8 +1466,11 @@
       <c r="K26" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L26" s="13">
+        <v>15.41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>19.2</v>
       </c>
@@ -1396,8 +1504,11 @@
       <c r="K27" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L27" s="13">
+        <v>17.05</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27.3</v>
       </c>
@@ -1431,8 +1542,11 @@
       <c r="K28" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L28" s="13">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -1466,8 +1580,11 @@
       <c r="K29" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L29" s="13">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>30.4</v>
       </c>
@@ -1501,8 +1618,11 @@
       <c r="K30" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L30" s="13">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>15.8</v>
       </c>
@@ -1536,8 +1656,11 @@
       <c r="K31" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L31" s="13">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>19.7</v>
       </c>
@@ -1571,8 +1694,11 @@
       <c r="K32" s="7">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L32" s="13">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>15</v>
       </c>
@@ -1606,8 +1732,11 @@
       <c r="K33" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L33" s="13">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>21.4</v>
       </c>
@@ -1641,8 +1770,11 @@
       <c r="K34" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L34" s="14">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1655,7 +1787,7 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>

--- a/tests/testthat/test_xlsx_files/data_to_worksheet.xlsx
+++ b/tests/testthat/test_xlsx_files/data_to_worksheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10119"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\code\xlr\tests\testthat\test_xlsx_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicholashilderson/Documents/Coding/xlr/tests/testthat/test_xlsx_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C4C65E-02CB-4F35-89E9-9F9B96B2CBDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00FD76F-61BF-CC4F-AA5A-43C2879AF27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test 1" sheetId="5" r:id="rId1"/>
@@ -20,45 +20,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="13">
-  <si>
-    <t>mpg</t>
-  </si>
-  <si>
-    <t>cyl</t>
-  </si>
-  <si>
-    <t>disp</t>
-  </si>
-  <si>
-    <t>hp</t>
-  </si>
-  <si>
-    <t>drat</t>
-  </si>
-  <si>
-    <t>wt</t>
-  </si>
-  <si>
-    <t>qsec</t>
-  </si>
-  <si>
-    <t>vs</t>
-  </si>
-  <si>
-    <t>am</t>
-  </si>
-  <si>
-    <t>gear</t>
-  </si>
-  <si>
-    <t>carb</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="14">
   <si>
     <t>test</t>
   </si>
   <si>
-    <t>scientific</t>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>test_r_numeric</t>
+  </si>
+  <si>
+    <t>test_r_integer</t>
+  </si>
+  <si>
+    <t>test_xlr_numeric</t>
+  </si>
+  <si>
+    <t>test_xlr_vector</t>
+  </si>
+  <si>
+    <t>test_xlr_numeric.1</t>
+  </si>
+  <si>
+    <t>test_xlr_percent</t>
+  </si>
+  <si>
+    <t>test_r_char</t>
+  </si>
+  <si>
+    <t>test_xlr_scientific</t>
+  </si>
+  <si>
+    <t>test_r_factor</t>
+  </si>
+  <si>
+    <t>test_r_complex</t>
+  </si>
+  <si>
+    <t>1+1i</t>
   </si>
 </sst>
 </file>
@@ -68,7 +71,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -96,13 +99,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -112,7 +108,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -138,41 +134,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -186,31 +155,27 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -223,6 +188,25 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F37171A-48B9-1F45-976F-C12CB11E1911}" name="table_test" displayName="table_test" ref="A2:J34" totalsRowShown="0">
+  <autoFilter ref="A2:J34" xr:uid="{2F37171A-48B9-1F45-976F-C12CB11E1911}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{BA6CD134-F555-CA44-8842-5F3FFBA55F41}" name="test_r_numeric"/>
+    <tableColumn id="2" xr3:uid="{45E38D07-4077-704D-8765-D070882FB80B}" name="test_r_integer"/>
+    <tableColumn id="3" xr3:uid="{22C78EF5-C3CF-844C-9587-1ABEB2985D06}" name="test_xlr_numeric"/>
+    <tableColumn id="4" xr3:uid="{9A9070B7-88D4-6146-AF3B-63A0048CD1D9}" name="test_xlr_vector"/>
+    <tableColumn id="5" xr3:uid="{79E2C61B-470A-F54A-9118-4204ADF836A5}" name="test_xlr_numeric.1"/>
+    <tableColumn id="6" xr3:uid="{55919E49-BE3E-1941-9EF7-664C70A15800}" name="test_xlr_percent"/>
+    <tableColumn id="7" xr3:uid="{FEE01BE1-3A4D-724E-B482-1B314186EF09}" name="test_r_char"/>
+    <tableColumn id="8" xr3:uid="{788DB702-7557-F244-A60B-0B169BC1E5AC}" name="test_xlr_scientific"/>
+    <tableColumn id="9" xr3:uid="{5AD8C718-73C0-FC4C-971B-80C3A4596CE9}" name="test_r_factor"/>
+    <tableColumn id="10" xr3:uid="{4E489EC6-FF30-8741-8FB7-490078D7F83A}" name="test_r_complex"/>
+  </tableColumns>
+  <tableStyleInfo name="none" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -504,1304 +488,1106 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L36"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="8">
         <v>21</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="9">
         <v>6</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>160</v>
       </c>
       <c r="D3" s="8">
         <v>110</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="6">
         <v>3.9</v>
       </c>
       <c r="F3" s="10">
         <v>2.62</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7">
         <v>16.46</v>
       </c>
-      <c r="H3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="7">
+      <c r="I3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="7">
-        <v>4</v>
-      </c>
-      <c r="K3" s="7">
-        <v>4</v>
-      </c>
-      <c r="L3" s="13">
-        <v>16.46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="J3" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="8">
         <v>21</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="9">
         <v>6</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>160</v>
       </c>
       <c r="D4" s="8">
         <v>110</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="6">
         <v>3.9</v>
       </c>
       <c r="F4" s="10">
         <v>2.875</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
         <v>17.02</v>
       </c>
-      <c r="H4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="7">
-        <v>1</v>
-      </c>
-      <c r="J4" s="7">
+      <c r="I4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="8">
+        <v>22.8</v>
+      </c>
+      <c r="B5" s="9">
         <v>4</v>
       </c>
-      <c r="K4" s="7">
-        <v>4</v>
-      </c>
-      <c r="L4" s="13">
-        <v>17.02</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>22.8</v>
-      </c>
-      <c r="B5" s="7">
-        <v>4</v>
-      </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>108</v>
       </c>
       <c r="D5" s="8">
         <v>93</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="6">
         <v>3.85</v>
       </c>
       <c r="F5" s="10">
         <v>2.3199999999999998</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
         <v>18.61</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="7">
+      <c r="I5" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="J5" s="7">
-        <v>4</v>
-      </c>
-      <c r="K5" s="7">
-        <v>1</v>
-      </c>
-      <c r="L5" s="13">
-        <v>18.61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="J5" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="8">
         <v>21.4</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>6</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>258</v>
       </c>
       <c r="D6" s="8">
         <v>110</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="6">
         <v>3.08</v>
       </c>
       <c r="F6" s="10">
         <v>3.2149999999999999</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
         <v>19.440000000000001</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="7">
-        <v>0</v>
-      </c>
-      <c r="J6" s="7">
-        <v>3</v>
-      </c>
-      <c r="K6" s="7">
-        <v>1</v>
-      </c>
-      <c r="L6" s="13">
-        <v>19.440000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+      <c r="I6" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="8">
         <v>18.7</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>8</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>360</v>
       </c>
       <c r="D7" s="8">
         <v>175</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="6">
         <v>3.15</v>
       </c>
       <c r="F7" s="10">
         <v>3.44</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
         <v>17.02</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="7">
-        <v>0</v>
-      </c>
-      <c r="J7" s="7">
-        <v>3</v>
-      </c>
-      <c r="K7" s="7">
-        <v>2</v>
-      </c>
-      <c r="L7" s="13">
-        <v>17.02</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="I7" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="8">
         <v>18.100000000000001</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="9">
         <v>6</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>225</v>
       </c>
       <c r="D8" s="8">
         <v>105</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="6">
         <v>2.76</v>
       </c>
       <c r="F8" s="10">
         <v>3.46</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
         <v>20.22</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="7">
-        <v>0</v>
-      </c>
-      <c r="J8" s="7">
-        <v>3</v>
-      </c>
-      <c r="K8" s="7">
-        <v>1</v>
-      </c>
-      <c r="L8" s="13">
-        <v>20.22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+      <c r="I8" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="8">
         <v>14.3</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="9">
         <v>8</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="5">
         <v>360</v>
       </c>
       <c r="D9" s="8">
         <v>245</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <v>3.21</v>
       </c>
       <c r="F9" s="10">
         <v>3.57</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
         <v>15.84</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="7">
-        <v>0</v>
-      </c>
-      <c r="J9" s="7">
-        <v>3</v>
-      </c>
-      <c r="K9" s="7">
+      <c r="I9" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="8">
+        <v>24.4</v>
+      </c>
+      <c r="B10" s="9">
         <v>4</v>
       </c>
-      <c r="L9" s="13">
-        <v>15.84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>24.4</v>
-      </c>
-      <c r="B10" s="7">
-        <v>4</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>146.69999999999999</v>
       </c>
       <c r="D10" s="8">
         <v>62</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <v>3.69</v>
       </c>
       <c r="F10" s="10">
         <v>3.19</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
         <v>20</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="7">
-        <v>0</v>
-      </c>
-      <c r="J10" s="7">
+      <c r="I10" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="8">
+        <v>22.8</v>
+      </c>
+      <c r="B11" s="9">
         <v>4</v>
       </c>
-      <c r="K10" s="7">
-        <v>2</v>
-      </c>
-      <c r="L10" s="13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>22.8</v>
-      </c>
-      <c r="B11" s="7">
-        <v>4</v>
-      </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <v>140.80000000000001</v>
       </c>
       <c r="D11" s="8">
         <v>95</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="6">
         <v>3.92</v>
       </c>
       <c r="F11" s="10">
         <v>3.15</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
         <v>22.9</v>
       </c>
-      <c r="H11" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="7">
-        <v>0</v>
-      </c>
-      <c r="J11" s="7">
-        <v>4</v>
-      </c>
-      <c r="K11" s="7">
-        <v>2</v>
-      </c>
-      <c r="L11" s="13">
-        <v>22.9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+      <c r="I11" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="8">
         <v>19.2</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="9">
         <v>6</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <v>167.6</v>
       </c>
       <c r="D12" s="8">
         <v>123</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="6">
         <v>3.92</v>
       </c>
       <c r="F12" s="10">
         <v>3.44</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
         <v>18.3</v>
       </c>
-      <c r="H12" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="7">
-        <v>0</v>
-      </c>
-      <c r="J12" s="7">
-        <v>4</v>
-      </c>
-      <c r="K12" s="7">
-        <v>4</v>
-      </c>
-      <c r="L12" s="13">
-        <v>18.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+      <c r="I12" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="8">
         <v>17.8</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="9">
         <v>6</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <v>167.6</v>
       </c>
       <c r="D13" s="8">
         <v>123</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="6">
         <v>3.92</v>
       </c>
       <c r="F13" s="10">
         <v>3.44</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7">
         <v>18.899999999999999</v>
       </c>
-      <c r="H13" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I13" s="7">
-        <v>0</v>
-      </c>
-      <c r="J13" s="7">
-        <v>4</v>
-      </c>
-      <c r="K13" s="7">
-        <v>4</v>
-      </c>
-      <c r="L13" s="13">
-        <v>18.899999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+      <c r="I13" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="8">
         <v>16.399999999999999</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="9">
         <v>8</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <v>275.8</v>
       </c>
       <c r="D14" s="8">
         <v>180</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="6">
         <v>3.07</v>
       </c>
       <c r="F14" s="10">
         <v>4.07</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7">
         <v>17.399999999999999</v>
       </c>
-      <c r="H14" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="7">
-        <v>0</v>
-      </c>
-      <c r="J14" s="7">
-        <v>3</v>
-      </c>
-      <c r="K14" s="7">
-        <v>3</v>
-      </c>
-      <c r="L14" s="13">
-        <v>17.399999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+      <c r="I14" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="8">
         <v>17.3</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="9">
         <v>8</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <v>275.8</v>
       </c>
       <c r="D15" s="8">
         <v>180</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="6">
         <v>3.07</v>
       </c>
       <c r="F15" s="10">
         <v>3.73</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
         <v>17.600000000000001</v>
       </c>
-      <c r="H15" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I15" s="7">
-        <v>0</v>
-      </c>
-      <c r="J15" s="7">
-        <v>3</v>
-      </c>
-      <c r="K15" s="7">
-        <v>3</v>
-      </c>
-      <c r="L15" s="13">
-        <v>17.600000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+      <c r="I15" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="8">
         <v>15.2</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="9">
         <v>8</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>275.8</v>
       </c>
       <c r="D16" s="8">
         <v>180</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="6">
         <v>3.07</v>
       </c>
       <c r="F16" s="10">
         <v>3.78</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7">
         <v>18</v>
       </c>
-      <c r="H16" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I16" s="7">
-        <v>0</v>
-      </c>
-      <c r="J16" s="7">
-        <v>3</v>
-      </c>
-      <c r="K16" s="7">
-        <v>3</v>
-      </c>
-      <c r="L16" s="13">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+      <c r="I16" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="8">
         <v>10.4</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="9">
         <v>8</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <v>472</v>
       </c>
       <c r="D17" s="8">
         <v>205</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="6">
         <v>2.93</v>
       </c>
       <c r="F17" s="10">
         <v>5.25</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7">
         <v>17.98</v>
       </c>
-      <c r="H17" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" s="7">
-        <v>0</v>
-      </c>
-      <c r="J17" s="7">
-        <v>3</v>
-      </c>
-      <c r="K17" s="7">
-        <v>4</v>
-      </c>
-      <c r="L17" s="13">
-        <v>17.98</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+      <c r="I17" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="8">
         <v>10.4</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="9">
         <v>8</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="5">
         <v>460</v>
       </c>
       <c r="D18" s="8">
         <v>215</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="6">
         <v>3</v>
       </c>
       <c r="F18" s="10">
         <v>5.4240000000000004</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7">
         <v>17.82</v>
       </c>
-      <c r="H18" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I18" s="7">
-        <v>0</v>
-      </c>
-      <c r="J18" s="7">
-        <v>3</v>
-      </c>
-      <c r="K18" s="7">
-        <v>4</v>
-      </c>
-      <c r="L18" s="13">
-        <v>17.82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+      <c r="I18" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="8">
         <v>14.7</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="9">
         <v>8</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="5">
         <v>440</v>
       </c>
       <c r="D19" s="8">
         <v>230</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="6">
         <v>3.23</v>
       </c>
       <c r="F19" s="10">
         <v>5.3449999999999998</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7">
         <v>17.420000000000002</v>
       </c>
-      <c r="H19" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I19" s="7">
-        <v>0</v>
-      </c>
-      <c r="J19" s="7">
-        <v>3</v>
-      </c>
-      <c r="K19" s="7">
+      <c r="I19" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="8">
+        <v>32.4</v>
+      </c>
+      <c r="B20" s="9">
         <v>4</v>
       </c>
-      <c r="L19" s="13">
-        <v>17.420000000000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>32.4</v>
-      </c>
-      <c r="B20" s="7">
-        <v>4</v>
-      </c>
-      <c r="C20" s="7">
+      <c r="C20" s="5">
         <v>78.7</v>
       </c>
       <c r="D20" s="8">
         <v>66</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="6">
         <v>4.08</v>
       </c>
       <c r="F20" s="10">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7">
         <v>19.47</v>
       </c>
-      <c r="H20" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I20" s="7">
-        <v>1</v>
-      </c>
-      <c r="J20" s="7">
+      <c r="I20" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="8">
+        <v>30.4</v>
+      </c>
+      <c r="B21" s="9">
         <v>4</v>
       </c>
-      <c r="K20" s="7">
-        <v>1</v>
-      </c>
-      <c r="L20" s="13">
-        <v>19.47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>30.4</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4</v>
-      </c>
-      <c r="C21" s="7">
+      <c r="C21" s="5">
         <v>75.7</v>
       </c>
       <c r="D21" s="8">
         <v>52</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="6">
         <v>4.93</v>
       </c>
       <c r="F21" s="10">
         <v>1.615</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7">
         <v>18.52</v>
       </c>
-      <c r="H21" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" s="7">
+      <c r="I21" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="J21" s="7">
+      <c r="J21" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="8">
+        <v>33.9</v>
+      </c>
+      <c r="B22" s="9">
         <v>4</v>
       </c>
-      <c r="K21" s="7">
-        <v>2</v>
-      </c>
-      <c r="L21" s="13">
-        <v>18.52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>33.9</v>
-      </c>
-      <c r="B22" s="7">
-        <v>4</v>
-      </c>
-      <c r="C22" s="7">
+      <c r="C22" s="5">
         <v>71.099999999999994</v>
       </c>
       <c r="D22" s="8">
         <v>65</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="6">
         <v>4.22</v>
       </c>
       <c r="F22" s="10">
         <v>1.835</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7">
         <v>19.899999999999999</v>
       </c>
-      <c r="H22" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" s="7">
-        <v>1</v>
-      </c>
-      <c r="J22" s="7">
+      <c r="I22" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="8">
+        <v>21.5</v>
+      </c>
+      <c r="B23" s="9">
         <v>4</v>
       </c>
-      <c r="K22" s="7">
-        <v>1</v>
-      </c>
-      <c r="L22" s="13">
-        <v>19.899999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>21.5</v>
-      </c>
-      <c r="B23" s="7">
-        <v>4</v>
-      </c>
-      <c r="C23" s="7">
+      <c r="C23" s="5">
         <v>120.1</v>
       </c>
       <c r="D23" s="8">
         <v>97</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="6">
         <v>3.7</v>
       </c>
       <c r="F23" s="10">
         <v>2.4649999999999999</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7">
         <v>20.010000000000002</v>
       </c>
-      <c r="H23" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I23" s="7">
-        <v>0</v>
-      </c>
-      <c r="J23" s="7">
-        <v>3</v>
-      </c>
-      <c r="K23" s="7">
+      <c r="I23" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="L23" s="13">
-        <v>20.010000000000002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+      <c r="J23" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="8">
         <v>15.5</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="9">
         <v>8</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="5">
         <v>318</v>
       </c>
       <c r="D24" s="8">
         <v>150</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="6">
         <v>2.76</v>
       </c>
       <c r="F24" s="10">
         <v>3.52</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7">
         <v>16.87</v>
       </c>
-      <c r="H24" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I24" s="7">
-        <v>0</v>
-      </c>
-      <c r="J24" s="7">
-        <v>3</v>
-      </c>
-      <c r="K24" s="7">
+      <c r="I24" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="L24" s="13">
-        <v>16.87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+      <c r="J24" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="8">
         <v>15.2</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="9">
         <v>8</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="5">
         <v>304</v>
       </c>
       <c r="D25" s="8">
         <v>150</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="6">
         <v>3.15</v>
       </c>
       <c r="F25" s="10">
         <v>3.4350000000000001</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H25" s="7">
         <v>17.3</v>
       </c>
-      <c r="H25" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I25" s="7">
-        <v>0</v>
-      </c>
-      <c r="J25" s="7">
-        <v>3</v>
-      </c>
-      <c r="K25" s="7">
-        <v>2</v>
-      </c>
-      <c r="L25" s="13">
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="I25" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
         <v>13.3</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="9">
         <v>8</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="5">
         <v>350</v>
       </c>
       <c r="D26" s="8">
         <v>245</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="6">
         <v>3.73</v>
       </c>
       <c r="F26" s="10">
         <v>3.84</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7">
         <v>15.41</v>
       </c>
-      <c r="H26" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I26" s="7">
-        <v>0</v>
-      </c>
-      <c r="J26" s="7">
-        <v>3</v>
-      </c>
-      <c r="K26" s="7">
-        <v>4</v>
-      </c>
-      <c r="L26" s="13">
-        <v>15.41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+      <c r="I26" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="8">
         <v>19.2</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="9">
         <v>8</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="5">
         <v>400</v>
       </c>
       <c r="D27" s="8">
         <v>175</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="6">
         <v>3.08</v>
       </c>
       <c r="F27" s="10">
         <v>3.8450000000000002</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="7">
         <v>17.05</v>
       </c>
-      <c r="H27" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I27" s="7">
-        <v>0</v>
-      </c>
-      <c r="J27" s="7">
-        <v>3</v>
-      </c>
-      <c r="K27" s="7">
-        <v>2</v>
-      </c>
-      <c r="L27" s="13">
-        <v>17.05</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
+      <c r="I27" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="8">
         <v>27.3</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="9">
         <v>4</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="5">
         <v>79</v>
       </c>
       <c r="D28" s="8">
         <v>66</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="6">
         <v>4.08</v>
       </c>
       <c r="F28" s="10">
         <v>1.9350000000000001</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7">
         <v>18.899999999999999</v>
       </c>
-      <c r="H28" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I28" s="7">
-        <v>1</v>
-      </c>
-      <c r="J28" s="7">
+      <c r="I28" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>26</v>
+      </c>
+      <c r="B29" s="9">
         <v>4</v>
       </c>
-      <c r="K28" s="7">
-        <v>1</v>
-      </c>
-      <c r="L28" s="13">
-        <v>18.899999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>26</v>
-      </c>
-      <c r="B29" s="7">
-        <v>4</v>
-      </c>
-      <c r="C29" s="7">
+      <c r="C29" s="5">
         <v>120.3</v>
       </c>
       <c r="D29" s="8">
         <v>91</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="6">
         <v>4.43</v>
       </c>
       <c r="F29" s="10">
         <v>2.14</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H29" s="7">
         <v>16.7</v>
       </c>
-      <c r="H29" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I29" s="7">
+      <c r="I29" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="J29" s="7">
-        <v>5</v>
-      </c>
-      <c r="K29" s="7">
-        <v>2</v>
-      </c>
-      <c r="L29" s="13">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+      <c r="J29" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
         <v>30.4</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="9">
         <v>4</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="5">
         <v>95.1</v>
       </c>
       <c r="D30" s="8">
         <v>113</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="6">
         <v>3.77</v>
       </c>
       <c r="F30" s="10">
         <v>1.5129999999999999</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H30" s="7">
         <v>16.899999999999999</v>
       </c>
-      <c r="H30" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I30" s="7">
-        <v>1</v>
-      </c>
-      <c r="J30" s="7">
-        <v>5</v>
-      </c>
-      <c r="K30" s="7">
+      <c r="I30" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="L30" s="13">
-        <v>16.899999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+      <c r="J30" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
         <v>15.8</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="9">
         <v>8</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="5">
         <v>351</v>
       </c>
       <c r="D31" s="8">
         <v>264</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="6">
         <v>4.22</v>
       </c>
       <c r="F31" s="10">
         <v>3.17</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H31" s="7">
         <v>14.5</v>
       </c>
-      <c r="H31" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I31" s="7">
+      <c r="I31" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="J31" s="7">
-        <v>5</v>
-      </c>
-      <c r="K31" s="7">
-        <v>4</v>
-      </c>
-      <c r="L31" s="13">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+      <c r="J31" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
         <v>19.7</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="9">
         <v>6</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="5">
         <v>145</v>
       </c>
       <c r="D32" s="8">
         <v>175</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="6">
         <v>3.62</v>
       </c>
       <c r="F32" s="10">
         <v>2.77</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7">
         <v>15.5</v>
       </c>
-      <c r="H32" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" s="7">
-        <v>1</v>
-      </c>
-      <c r="J32" s="7">
-        <v>5</v>
-      </c>
-      <c r="K32" s="7">
-        <v>6</v>
-      </c>
-      <c r="L32" s="13">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+      <c r="I32" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
         <v>15</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="9">
         <v>8</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="5">
         <v>301</v>
       </c>
       <c r="D33" s="8">
         <v>335</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="6">
         <v>3.54</v>
       </c>
       <c r="F33" s="10">
         <v>3.57</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H33" s="7">
         <v>14.6</v>
       </c>
-      <c r="H33" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I33" s="7">
+      <c r="I33" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="J33" s="7">
-        <v>5</v>
-      </c>
-      <c r="K33" s="7">
-        <v>8</v>
-      </c>
-      <c r="L33" s="13">
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+      <c r="J33" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
         <v>21.4</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="9">
         <v>4</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="5">
         <v>121</v>
       </c>
       <c r="D34" s="8">
         <v>109</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="6">
         <v>4.1100000000000003</v>
       </c>
       <c r="F34" s="10">
         <v>2.78</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7">
         <v>18.600000000000001</v>
       </c>
-      <c r="H34" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" s="7">
-        <v>1</v>
-      </c>
-      <c r="J34" s="7">
-        <v>4</v>
-      </c>
-      <c r="K34" s="7">
+      <c r="I34" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="L34" s="14">
-        <v>18.600000000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
+      <c r="J34" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>